--- a/daily_matches/job_matches_2026-09-24.xlsx
+++ b/daily_matches/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>33.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0cab26aeb02c83</t>
+          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>eHealth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>31.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, Copilot, S3, Glue, Redshift, BigQuery, Kinesis, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9741dbb2ec8505fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2f6705aae6b6275d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Korean Bilingual Jr. AI Developer</t>
+          <t>SPEC ADV SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7384cdf34c3a1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54cc75b0d6eba6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tekmetric</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, PyTorch, XGBoost, S3</t>
+          <t>AI Engineer, LangChain, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a562a6784ed8a2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad026bf190602503</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
+          <t>Senior Software Engineer â€“ Application Reliability (Kubernetes, GCP, SQL), Hybrid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, BigQuery, Kubernetes, CI/CD, Git, Databricks, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Kubernetes, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a525da0163d7e9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack AI Engineer (Agentic Systems)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cinemark</t>
+          <t>Quzara LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=08fa92c6142cdf51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/AWS)</t>
+          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PySpark, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9afa06dd2d2419</t>
+          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>AI Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Kinesis, Docker, Kubernetes, CI/CD, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5e36ccada321d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Software Engineer II (Credit)</t>
+          <t>Senior Performance Engineer- JMeter, JavaScript - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d903bccdbf3972</t>
+          <t>https://www.indeed.com/viewjob?jk=e07c1b1495c7e476</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Security Automation Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity National Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e83fb76d1c2060</t>
+          <t>https://www.indeed.com/viewjob?jk=7efd057917fe722a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Copilot, S3, Terraform, Git, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173ce97c51fac63</t>
+          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>All IT Solutions LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Tableau, R</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ba5f938307691</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
+          <t>https://www.indeed.com/viewjob?jk=07ab92a39cc8b69e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, CI/CD, Snowflake, Power BI, Matplotlib, Python, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e622377cb7d33c2a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Palantir IT Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Korean Bilingual Sr. AI DevOps Developer</t>
+          <t>AI Programmer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a20f91581ba7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1b0c3b4924cd1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Dataflow, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Architect</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>CareConnectMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+          <t>Docker, Kubernetes, Jenkins, Git, MySQL, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3b5469001cd010</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7813a197312f0dd5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f8023b61ed2239</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Risk Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb5d4be7f6f56d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Service Supply Chain AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0260ffc993b02808</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Fullstack AI Engineer (Generative AI / Agentic Systems)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244900bbd13e69cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Platform Developer</t>
+          <t>Senior Java Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Copilot, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8014df740d3df704</t>
+          <t>https://www.indeed.com/viewjob?jk=e1aa69f0ea5e6d50</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Associate AI Engineer, OI&amp;A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Kafka, Hadoop, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, AKS, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c94b5498484e7a3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Arena</t>
+          <t>AI / DevOps Engineer – Agentic Systems &amp; Automation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136719f380319c28</t>
+          <t>https://www.indeed.com/viewjob?jk=e99566c4fc7a131f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Sport &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Snowflake, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8713f4e92a93df0</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a3e6c744c20fd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Snowflake, Databricks, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, GitHub Actions, Git, Databricks, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174ab9eaee58aad1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d35a8e890e5574</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Marketing Analytics</t>
+          <t>Software Engineer, CX(Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6230809ab9de857</t>
+          <t>https://www.indeed.com/viewjob?jk=c99aa5ec0b3c2d05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Applied AI Scientist</t>
+          <t>Senior Software Engineer, Frontend</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Git, Python, R</t>
+          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac71e5a13bd6fd91</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8b5f045d6c8c40</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Research Software Engineer</t>
+          <t>Data Product Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, MySQL, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,672 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8521a603d24c1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Copilot, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a452d465e71ecc</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Identity Digital</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Glue, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b468d5dbbf0d446</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer - Digital Workplace Automation</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NextEra Energy</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=164f97f1873686d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Renaissance Learning</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Wisconsin Rapids, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd521a2fa445a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe2d86025f5b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Cloud Operations Engineer - AI Cloud Ops</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=582efefa3eef65ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Evinova</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>AstraZeneca</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Gaithersburg, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8705d8e844c6e444</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Goodwin Procter LLP</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b23d702d0d737a35</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Sr. AI Voice Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nowcom, LLC</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e567a4436f83eb6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Software Engineer (Android / iOS)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe31fb6302f2ab9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>T. Rowe Price</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>S3, CI/CD, Snowflake, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>INTERNSHIP - SOLIDWORKS RELOPS</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SolidWorks</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Docker, CI/CD, Jenkins, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0228e73951d0994c</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer – Databricks</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Optimal Inc.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, MLflow, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4874119a54732db7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Release and Performance Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fdc276eac533a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Data Scientist, EHR &amp; PMS Integrations</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Liine</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Athena, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b4597971fb3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Associate Enterprise Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499c21c2e59cd41e</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer, Platform</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30894be4e5dc8c9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Scientist - Space Intelligence</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4aa1b4d9d86e6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Fraud Detection</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>DataVisor</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83c25cad41fb9f24</t>
+          <t>https://www.indeed.com/viewjob?jk=4f80c5ba4d64f199</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-24.xlsx
+++ b/daily_matches/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/Data Science Eng I</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.3</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, RAG, Cortex, TensorFlow, PyTorch, S3, EC2, Redshift, BigQuery, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e200e28931966534</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eHealth</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Glue, Redshift, BigQuery, Kinesis, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f6705aae6b6275d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPEC ADV SOFTWARE ENGINEER</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54cc75b0d6eba6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,172 +601,172 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee726419802dccd3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad026bf190602503</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer â€“ Application Reliability (Kubernetes, GCP, SQL), Hybrid</t>
+          <t>Sr. Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Silicon Labs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Kubernetes, Git, BigQuery, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a525da0163d7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full-Stack AI Engineer (Agentic Systems)</t>
+          <t>Backend Engineer: Retail Media</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quzara LLC</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Athena, FastAPI, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08fa92c6142cdf51</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Git, Kafka, NoSQL, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+          <t>https://www.indeed.com/viewjob?jk=464f070dcc86c2c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer 4</t>
+          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Kinesis, Docker, Kubernetes, CI/CD, Databricks, Kafka</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5e36ccada321d</t>
+          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Performance Engineer- JMeter, JavaScript - Remote</t>
+          <t>Senior DevOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>AltexSoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,46 +797,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07c1b1495c7e476</t>
+          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efd057917fe722a</t>
+          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Terraform, Git, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ba5f938307691</t>
+          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07ab92a39cc8b69e</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Snowflake, Power BI, Matplotlib, Python, R, Optimization, A/B Testing</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622377cb7d33c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Palantir IT Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Programmer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1b0c3b4924cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CareConnectMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Git, MySQL, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Engineer 4 - MLOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Dask, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f8023b61ed2239</t>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Risk Analyst</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb5d4be7f6f56d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Service Supply Chain AI Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0260ffc993b02808</t>
+          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Kubernetes, CI/CD, Dask, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1aa69f0ea5e6d50</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate AI Engineer, OI&amp;A</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, AKS, CI/CD, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c94b5498484e7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI / DevOps Engineer – Agentic Systems &amp; Automation</t>
+          <t>Full-stack Engineer 4, Tech College Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99566c4fc7a131f</t>
+          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Sport &amp; Data Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chester, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a3e6c744c20fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer Associate</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, CI/CD, GitHub Actions, Git, Databricks, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d35a8e890e5574</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, CX(Hybrid)</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Kubernetes, CI/CD, Dask, Python, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99aa5ec0b3c2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,882 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8b5f045d6c8c40</t>
+          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Backend Python/Databricks Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Apache Airflow, CI/CD, Terraform, Databricks, PySpark, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Healthcare Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wider Circle</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Junior Integration Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Consertus</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Guaynabo, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Git, BigQuery, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Adobe</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, Jenkins, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=882f57482f534234</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - CloudOps</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AAA Auto Club Enterprises</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=071f9e85e7ae21bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc27d0c968f28ebb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9e17e48b8eb913e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Kafka, Hadoop, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0f345f05b076e3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Azure Databricks Administrator</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Technical Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f80c5ba4d64f199</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Git, Kafka, Cassandra, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6046a872257c23f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, Prompt Engineering, Databricks, Tableau, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a892e25bc8b87dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Prompt Engineering, Databricks, Tableau, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbc1155630a772</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Solutions/Software Analyst/Scientist/Engineer - Workflow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fulgent Therapeutics</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>El Monte, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Git, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbaa82e2206e2dd0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-24.xlsx
+++ b/daily_matches/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Linux Administrator (Infrastructure)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Copilot, S3, Glue, Redshift, BigQuery, Kinesis, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0078f92c43fa36</t>
+          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Linux Administrator (Infrastructure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, FastAPI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f96013110cf486</t>
+          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linux Administrator (Ops)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa8b81839324a01</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c7d9bcaaeb50a7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Linux Administrator (Ops)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034adc8fdcd3f32</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer – AI</t>
+          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Menrva Group</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LLaMA, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MongoDB</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b9b338e1b4e1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Industry 4.0 / AI &amp; IoT</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Kafka, Python</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b685f9437e6b7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031736ee0bc1b915</t>
+          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bates White Economic Consulting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, MLflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f332a8477897f8e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, FastAPI, CI/CD, Terraform, NoSQL, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b908ded2ecce8195</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, CI/CD, Terraform, Git, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
+          <t>https://www.indeed.com/viewjob?jk=f11f04cc218fd91c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94584dbdf31f9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=de05f9c575d914fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, EC2, Data Lake, Kubernetes, CI/CD, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4ce506118a2862</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ThoughtFocus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, Data Lake, Snowflake, PySpark, MySQL, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817fd883bd585f22</t>
+          <t>https://www.indeed.com/viewjob?jk=5e52d983dd64d153</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer - Generative AI &amp; Intelligent Automation (contract)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OrthoFi</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Kubernetes, Kafka, MongoDB, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ef4a9f676f51a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef5e0a86f206ef9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, FastAPI, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b9338700a48d82</t>
+          <t>https://www.indeed.com/viewjob?jk=cabd2a3b4db04ae7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Ruby on Rails</t>
+          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,567 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edbb34ea322379</t>
+          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Oats Overnight</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Syngenta</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b161240b7c2e92f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Docker, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a03a0f1c76f495bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer I (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Docker, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c14f27a2967cdb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer Data &amp; AI II (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b674f07a8e151c6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, OpenCV, YOLO, Docker, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0532da8a5787d1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cloud Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Barracuda Networks</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1496eec1f94e339</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Peloton</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08f7f2c6ba6ec204</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior AI Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7799bf473f312b17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Forecasting Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aec7614e2beba7b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Science Analyst - Growth, Marketing &amp; Sales Practice</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, MongoDB, NoSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=067553b5bdbabc80</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer - Product Development</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Athena, Kinesis, Terraform, Git, Databricks, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1c6d106df61ae</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2727fd188c1ee88f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer - Sr Consultant level-2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38e23654409b469c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (.NET), Telephony</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DriveCentric</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d18c5fb27732fff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Service Delivery Center - Senior - IBM APIC Platform Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5feab679ff43dd0c</t>
         </is>
       </c>
     </row>
